--- a/etf_holdings/2026-09-18_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-18_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,6 +1806,114 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>215000</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-17_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2150000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-450,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-17_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf_holdings/2026-09-18_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-18_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,114 +1806,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>215000</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-09-17_00992A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2.78%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2.29%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-0.49%</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>2150000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-450,000</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-09-17_00992A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
